--- a/data/trans_bre/P1423-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1423-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,27</t>
+          <t>3,99; 8,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,65; 15,05</t>
+          <t>9,53; 14,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,75; 14,44</t>
+          <t>8,89; 14,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,91; 12,25</t>
+          <t>5,23; 11,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>61,57; 192,86</t>
+          <t>58,96; 192,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>114,05; 271,6</t>
+          <t>113,64; 259,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>132,09; 343,98</t>
+          <t>135,9; 372,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>46,46; 136,11</t>
+          <t>39,72; 135,16</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 5,07</t>
+          <t>2,32; 5,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,85</t>
+          <t>2,84; 6,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,43; 7,35</t>
+          <t>4,25; 7,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 7,23</t>
+          <t>2,36; 7,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>93,96; 339,08</t>
+          <t>92,21; 346,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,29; 230,7</t>
+          <t>73,52; 239,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>123,08; 303,9</t>
+          <t>126,34; 304,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,17; 207,51</t>
+          <t>46,42; 206,59</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 4,01</t>
+          <t>-0,6; 4,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,66</t>
+          <t>-1,42; 3,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 3,31</t>
+          <t>-0,97; 3,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 4,64</t>
+          <t>-0,45; 4,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-22,43; 204,46</t>
+          <t>-21,69; 219,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,83; 205,7</t>
+          <t>-42,48; 199,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-35,77; 288,23</t>
+          <t>-40,27; 289,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 121,42</t>
+          <t>-9,08; 115,05</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 5,61</t>
+          <t>3,4; 5,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,96; 8,57</t>
+          <t>6,02; 8,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,59; 8,08</t>
+          <t>5,69; 8,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,43; 7,19</t>
+          <t>3,4; 7,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,3; 209,38</t>
+          <t>95,87; 207,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>126,09; 238,21</t>
+          <t>125,8; 239,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>149,54; 289,85</t>
+          <t>154,54; 279,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58,43; 155,37</t>
+          <t>56,31; 148,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P1423-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1423-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,86</t>
+          <t>10,02</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>101,53%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 8,43</t>
+          <t>3,9; 8,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,53; 14,9</t>
+          <t>9,6; 15,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,89; 14,98</t>
+          <t>8,58; 14,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,23; 11,93</t>
+          <t>6,51; 13,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>58,96; 192,97</t>
+          <t>63,36; 197,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>113,64; 259,49</t>
+          <t>112,41; 259,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>135,9; 372,57</t>
+          <t>126,97; 359,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39,72; 135,16</t>
+          <t>54,14; 168,52</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,98</t>
+          <t>5,65</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>104,63%</t>
+          <t>104,9%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,02</t>
+          <t>2,31; 4,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 6,01</t>
+          <t>2,89; 5,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,25; 7,24</t>
+          <t>4,37; 7,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 7,26</t>
+          <t>4,09; 7,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>92,21; 346,49</t>
+          <t>89,26; 341,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,52; 239,62</t>
+          <t>78,32; 234,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>126,34; 304,18</t>
+          <t>124,75; 316,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,42; 206,59</t>
+          <t>67,53; 156,18</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>1,87</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>35,25%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 4,3</t>
+          <t>-0,65; 3,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 3,39</t>
+          <t>-1,47; 3,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 3,28</t>
+          <t>-0,71; 3,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 4,59</t>
+          <t>-0,86; 4,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 219,51</t>
+          <t>-22,76; 215,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-42,48; 199,12</t>
+          <t>-39,52; 209,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-40,27; 289,15</t>
+          <t>-34,86; 302,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 115,05</t>
+          <t>-13,15; 119,77</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,57</t>
+          <t>6,12</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>100,22%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 5,59</t>
+          <t>3,38; 5,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,02; 8,57</t>
+          <t>5,99; 8,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,69; 8,03</t>
+          <t>5,66; 8,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 7,18</t>
+          <t>4,77; 7,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,87; 207,45</t>
+          <t>94,2; 210,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>125,8; 239,59</t>
+          <t>126,68; 245,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>154,54; 279,73</t>
+          <t>151,84; 286,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>56,31; 148,36</t>
+          <t>70,62; 132,16</t>
         </is>
       </c>
     </row>
